--- a/tests/realSuite/Piano-Viaggi-Corsa-Campestre_IS_12-marzo-25_con-cel-3/input.xlsx
+++ b/tests/realSuite/Piano-Viaggi-Corsa-Campestre_IS_12-marzo-25_con-cel-3/input.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:C18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -481,181 +481,211 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>IS Degasperi</t>
+          <t>IS Da Vinci</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Stazione autocorriere, Borgo Valsugana</t>
+          <t>Fermata Bus davanti cinema Modena, Piazza Venezia, Trento</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>IS Enaip Tesero</t>
+          <t>IS Degasperi</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Piazza C. Battisti, Tesero</t>
+          <t>Stazione autocorriere, Borgo Valsugana</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>IS Floriani</t>
+          <t>IS Enaip Tesero</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Scuola - Viale dei Tigli, 43, Riva del Garda</t>
+          <t>Piazza C. Battisti, Tesero</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>IS Guetti</t>
+          <t>IS Floriani</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Scuole – Via Durone, Tione</t>
+          <t>Scuola - Viale dei Tigli, 43, Riva del Garda</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>30</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>IS Ladino di Fassa</t>
+          <t>IS Guetti</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Via G. Soraperra, 6, Sèn Jan/San Giovanni</t>
+          <t>Scuole – Via Durone, Tione</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>14</v>
+        <v>30</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>IS Levico Termico Alberghiero</t>
+          <t>IS Ladino di Fassa</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Fermata Bus rotatoria Corso Rovigo, Levico Terme</t>
+          <t>Via G. Soraperra, 6, Sèn Jan/San Giovanni</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>IS Maffei</t>
+          <t>IS Levico Termico Alberghiero</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>c/o SSPG - Via D. Chiesa, 10, Riva del Garda</t>
+          <t>Fermata Bus rotatoria Corso Rovigo, Levico Terme</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>27</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>IS Martini + Students Staff</t>
+          <t>IS Maffei</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>c/o IS Martini - Via Perlasca 4, Mezzolombardo</t>
+          <t>c/o SSPG - Via D. Chiesa, 10, Riva del Garda</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>13</v>
+        <v>27</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>IS Pertini</t>
+          <t>IS Martini + Students Staff</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Fermata Bus San Bartolomeo, Viale Verona 17, Trento</t>
+          <t>c/o IS Martini - Via Perlasca 4, Mezzolombardo</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>IS Pilati</t>
+          <t>IS Pertini</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Scuola – Via IV Novembre, Cles</t>
+          <t>Fermata Bus San Bartolomeo, Viale Verona 17, Trento</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>IS Prati</t>
+          <t>IS Pilati</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Fermata Funivia - Lungadige, Trento</t>
+          <t>Scuola – Via IV Novembre, Cles</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>IS Prati</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Fermata Funivia - Lungadige, Trento</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>IS Primiero</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>Stazione autocorriere, Fiera di Primiero</t>
         </is>
       </c>
-      <c r="C16" t="n">
+      <c r="C17" t="n">
         <v>27</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>IS Tione Enaip</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Scuole – Via Durone, Tione</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
